--- a/Modelos/TRE-JULHO-2026.xlsx
+++ b/Modelos/TRE-JULHO-2026.xlsx
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30417"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{106E5591-FE85-4238-A4B1-8382944B078C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A788980-2BF2-475B-8B41-80FAAB059CE6}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sicoobjuriscredcelgbr-my.sharepoint.com/personal/reginaldo_sousa_sicoobjuriscred_com_br/Documents/Arquivos de Chat do Microsoft Teams/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{6CAAE60A-2CC1-4C7B-AE6C-D25D24117DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{501DEF93-BB9B-4844-80D6-02A8A38D2288}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4159103A-EFA0-41AB-BE61-18FC98C346F6}"/>
   </bookViews>
   <sheets>
-    <sheet name="LANÇAMENTOS" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LANÇAMENTOS!$A$2:$E$2</definedName>
-  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,46 +36,130 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>EXTRATO CONTA CORRENTE</t>
-  </si>
-  <si>
-    <t>DATA</t>
-  </si>
-  <si>
-    <t>DOCUMENTO</t>
-  </si>
-  <si>
-    <t>HISTÓRICO</t>
-  </si>
-  <si>
-    <t>INFORMAÇÕES COMPLEMENTARES</t>
-  </si>
-  <si>
-    <t>VALOR</t>
-  </si>
-  <si>
-    <t>21/08/2026</t>
-  </si>
-  <si>
-    <t>372566120</t>
-  </si>
-  <si>
-    <t>CRÉD.TED-STR</t>
-  </si>
-  <si>
-    <t>TRIBUNAL REGIONAL ELEITORAL DE GOIAS
-05.526.875 0001-45
-CODIGO TED: T1087236908
-20260044009670000000</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="38">
+  <si>
+    <t>Matrícula</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>CPF</t>
+  </si>
+  <si>
+    <t>Situação</t>
+  </si>
+  <si>
+    <t>Rubrica</t>
+  </si>
+  <si>
+    <t>Descrição</t>
+  </si>
+  <si>
+    <t>Mês/Ano Referência</t>
+  </si>
+  <si>
+    <t>Prazo</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>5069629</t>
+  </si>
+  <si>
+    <t>BENEDITO DA COSTA VELOSO FILHO</t>
+  </si>
+  <si>
+    <t>22210105153</t>
+  </si>
+  <si>
+    <t>ATIVO</t>
+  </si>
+  <si>
+    <t>6191.000</t>
+  </si>
+  <si>
+    <t>EMPRÉSTIMO COOPERATIVA DE CRÉDITO - SICOOB</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>3944,41</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>5731,94</t>
+  </si>
+  <si>
+    <t>5067251</t>
+  </si>
+  <si>
+    <t>MARIA DE LOURDES MACEDO DE ANDRADE</t>
+  </si>
+  <si>
+    <t>26360896168</t>
+  </si>
+  <si>
+    <t>084</t>
+  </si>
+  <si>
+    <t>516,28</t>
+  </si>
+  <si>
+    <t>5067120</t>
+  </si>
+  <si>
+    <t>JORGE MARCOS DE SOUZA</t>
+  </si>
+  <si>
+    <t>92928870849</t>
+  </si>
+  <si>
+    <t>INATIVO</t>
+  </si>
+  <si>
+    <t>083</t>
+  </si>
+  <si>
+    <t>620,63</t>
+  </si>
+  <si>
+    <t>6198.000</t>
+  </si>
+  <si>
+    <t>EMPRÉSTIMO COOPERATIVA - SICOOB - MARGEM 5%</t>
+  </si>
+  <si>
+    <t>082</t>
+  </si>
+  <si>
+    <t>61,1</t>
+  </si>
+  <si>
+    <t>079</t>
+  </si>
+  <si>
+    <t>270,49</t>
+  </si>
+  <si>
+    <t>087</t>
+  </si>
+  <si>
+    <t>453,9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00_);\(#,##0.00\)"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,39 +167,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99CCFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -128,25 +188,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -177,44 +236,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -242,14 +301,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -277,6 +353,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -288,266 +381,379 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFF5D46D-7206-469C-854B-D6365FC4523B}">
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>5</v>
+    <row r="2" spans="1:9">
+      <c r="A2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="6"/>
+      <c r="H2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="60">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="5" t="s">
+    <row r="3" spans="1:9">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="6">
-        <v>11598.75</v>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 #PÚBLICA#</oddFooter>
   </headerFooter>
@@ -555,31 +761,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2c321211-d78a-4511-b472-046c88e8b100">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="823753a6-0c53-4a85-b295-69bde1c537d8" xsi:nil="true"/>
-    <_dlc_DocId xmlns="823753a6-0c53-4a85-b295-69bde1c537d8">SEEJH4QPNV7R-54099711-1762647</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="823753a6-0c53-4a85-b295-69bde1c537d8">
-      <Url>https://sicoobjuriscredcelgbr.sharepoint.com/sites/PortaldeDocumentosSicoobJuriscred/_layouts/15/DocIdRedir.aspx?ID=SEEJH4QPNV7R-54099711-1762647</Url>
-      <Description>SEEJH4QPNV7R-54099711-1762647</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -629,7 +810,7 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002E02EC0FC915274D88E73E4D287B9C9B" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f89bc721952bf93ca5ee561089b0a2d6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="823753a6-0c53-4a85-b295-69bde1c537d8" xmlns:ns3="2c321211-d78a-4511-b472-046c88e8b100" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1061a565f16dc2d7434ea6b6956539a8" ns2:_="" ns3:_="">
     <xsd:import namespace="823753a6-0c53-4a85-b295-69bde1c537d8"/>
@@ -861,20 +1042,45 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2c321211-d78a-4511-b472-046c88e8b100">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="823753a6-0c53-4a85-b295-69bde1c537d8" xsi:nil="true"/>
+    <_dlc_DocId xmlns="823753a6-0c53-4a85-b295-69bde1c537d8">SEEJH4QPNV7R-54099711-1762650</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="823753a6-0c53-4a85-b295-69bde1c537d8">
+      <Url>https://sicoobjuriscredcelgbr.sharepoint.com/sites/PortaldeDocumentosSicoobJuriscred/_layouts/15/DocIdRedir.aspx?ID=SEEJH4QPNV7R-54099711-1762650</Url>
+      <Description>SEEJH4QPNV7R-54099711-1762650</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C244DCB2-CDC1-4323-84AE-F552073AA183}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3CF69D4-3DD4-4A04-9693-48DE9C1ADB3B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D36F227B-F0BC-4062-B416-980AF5BEAEC2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FED06C7-4D18-404C-83C8-FC52F17F1D29}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4D8C2B4-A9CE-4490-9ADB-83FE214EA85D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FD1C72C-4FBE-48B1-A185-6223B8132864}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{749144C5-8690-43BD-A0D0-5471D49043E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57678646-00FF-4D9D-819E-97C52AF62DB2}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
